--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -11708,17 +11708,17 @@
         <v>1</v>
       </c>
       <c r="E337" s="1"/>
-      <c r="F337" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G337" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H337" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F337" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2380.0)</f>
+        <v>2380</v>
+      </c>
+      <c r="G337" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
+      </c>
+      <c r="H337" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.57142857142857)</f>
+        <v>48.57142857</v>
       </c>
     </row>
     <row r="338">
@@ -11739,17 +11739,17 @@
         <v>2</v>
       </c>
       <c r="E338" s="1"/>
-      <c r="F338" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G338" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H338" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F338" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3015.02)</f>
+        <v>3015.02</v>
+      </c>
+      <c r="G338" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71.0)</f>
+        <v>71</v>
+      </c>
+      <c r="H338" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.46507042253521)</f>
+        <v>42.46507042</v>
       </c>
     </row>
     <row r="339">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -11770,17 +11770,17 @@
         <v>1</v>
       </c>
       <c r="E339" s="1"/>
-      <c r="F339" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G339" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H339" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F339" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3900.5)</f>
+        <v>3900.5</v>
+      </c>
+      <c r="G339" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.0)</f>
+        <v>90</v>
+      </c>
+      <c r="H339" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.33888888888889)</f>
+        <v>43.33888889</v>
       </c>
     </row>
     <row r="340">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -11801,17 +11801,17 @@
         <v>2</v>
       </c>
       <c r="E340" s="1"/>
-      <c r="F340" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G340" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H340" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F340" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2976.01)</f>
+        <v>2976.01</v>
+      </c>
+      <c r="G340" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.0)</f>
+        <v>65</v>
+      </c>
+      <c r="H340" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.784769230769236)</f>
+        <v>45.78476923</v>
       </c>
     </row>
     <row r="341">
@@ -11832,17 +11832,17 @@
         <v>1</v>
       </c>
       <c r="E341" s="1"/>
-      <c r="F341" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G341" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H341" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F341" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4037.5)</f>
+        <v>4037.5</v>
+      </c>
+      <c r="G341" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.0)</f>
+        <v>89</v>
+      </c>
+      <c r="H341" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.36516853932584)</f>
+        <v>45.36516854</v>
       </c>
     </row>
     <row r="342">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -11863,17 +11863,17 @@
         <v>2</v>
       </c>
       <c r="E342" s="1"/>
-      <c r="F342" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G342" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H342" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F342" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3251.01)</f>
+        <v>3251.01</v>
+      </c>
+      <c r="G342" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),87.0)</f>
+        <v>87</v>
+      </c>
+      <c r="H342" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.36793103448276)</f>
+        <v>37.36793103</v>
       </c>
     </row>
     <row r="343">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -11676,7 +11676,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E336" s="1"/>
+      <c r="E336" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
+        <v>2356.85</v>
+      </c>
       <c r="F336" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3679.0)</f>
         <v>3679</v>
@@ -11707,7 +11710,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E337" s="1"/>
+      <c r="E337" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
+        <v>2287.03</v>
+      </c>
       <c r="F337" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2380.0)</f>
         <v>2380</v>
@@ -11738,7 +11744,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E338" s="1"/>
+      <c r="E338" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
+        <v>2757.4</v>
+      </c>
       <c r="F338" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3015.02)</f>
         <v>3015.02</v>
@@ -11769,7 +11778,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E339" s="1"/>
+      <c r="E339" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
+        <v>3129.21</v>
+      </c>
       <c r="F339" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3900.5)</f>
         <v>3900.5</v>
@@ -11800,18 +11812,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E340" s="1"/>
-      <c r="F340" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G340" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H340" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="E340" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
+        <v>2824.96</v>
+      </c>
+      <c r="F340" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2976.01)</f>
+        <v>2976.01</v>
+      </c>
+      <c r="G340" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.0)</f>
+        <v>65</v>
+      </c>
+      <c r="H340" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.784769230769236)</f>
+        <v>45.78476923</v>
       </c>
     </row>
     <row r="341">
@@ -11831,18 +11846,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E341" s="1"/>
-      <c r="F341" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G341" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H341" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="E341" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
+        <v>3969.19</v>
+      </c>
+      <c r="F341" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4037.5)</f>
+        <v>4037.5</v>
+      </c>
+      <c r="G341" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.0)</f>
+        <v>89</v>
+      </c>
+      <c r="H341" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.36516853932584)</f>
+        <v>45.36516854</v>
       </c>
     </row>
     <row r="342">
@@ -11862,18 +11880,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E342" s="1"/>
-      <c r="F342" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G342" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H342" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="E342" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
+        <v>4064.6</v>
+      </c>
+      <c r="F342" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3251.01)</f>
+        <v>3251.01</v>
+      </c>
+      <c r="G342" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),87.0)</f>
+        <v>87</v>
+      </c>
+      <c r="H342" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.36793103448276)</f>
+        <v>37.36793103</v>
       </c>
     </row>
     <row r="343">
@@ -11893,7 +11914,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E343" s="1"/>
+      <c r="E343" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
+        <v>2356.85</v>
+      </c>
       <c r="F343" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -11924,7 +11948,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E344" s="1"/>
+      <c r="E344" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
+        <v>2287.03</v>
+      </c>
       <c r="F344" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -11955,7 +11982,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E345" s="1"/>
+      <c r="E345" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
+        <v>2757.4</v>
+      </c>
       <c r="F345" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -11986,7 +12016,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E346" s="1"/>
+      <c r="E346" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
+        <v>3129.21</v>
+      </c>
       <c r="F346" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12017,7 +12050,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E347" s="1"/>
+      <c r="E347" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
+        <v>2824.96</v>
+      </c>
       <c r="F347" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12048,7 +12084,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E348" s="1"/>
+      <c r="E348" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
+        <v>3969.19</v>
+      </c>
       <c r="F348" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12079,7 +12118,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E349" s="1"/>
+      <c r="E349" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
+        <v>4064.6</v>
+      </c>
       <c r="F349" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12110,7 +12152,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E350" s="1"/>
+      <c r="E350" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
+        <v>2356.85</v>
+      </c>
       <c r="F350" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12141,7 +12186,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E351" s="1"/>
+      <c r="E351" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
+        <v>2287.03</v>
+      </c>
       <c r="F351" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12172,7 +12220,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E352" s="1"/>
+      <c r="E352" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
+        <v>2757.4</v>
+      </c>
       <c r="F352" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12203,7 +12254,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E353" s="1"/>
+      <c r="E353" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
+        <v>3129.21</v>
+      </c>
       <c r="F353" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12234,7 +12288,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E354" s="1"/>
+      <c r="E354" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
+        <v>2824.96</v>
+      </c>
       <c r="F354" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12265,7 +12322,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E355" s="1"/>
+      <c r="E355" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
+        <v>3969.19</v>
+      </c>
       <c r="F355" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12296,7 +12356,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E356" s="1"/>
+      <c r="E356" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
+        <v>4064.6</v>
+      </c>
       <c r="F356" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12327,7 +12390,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E357" s="1"/>
+      <c r="E357" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
+        <v>2356.85</v>
+      </c>
       <c r="F357" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12358,7 +12424,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E358" s="1"/>
+      <c r="E358" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
+        <v>2287.03</v>
+      </c>
       <c r="F358" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12389,7 +12458,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E359" s="1"/>
+      <c r="E359" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
+        <v>2757.4</v>
+      </c>
       <c r="F359" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12420,7 +12492,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E360" s="1"/>
+      <c r="E360" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
+        <v>3129.21</v>
+      </c>
       <c r="F360" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12451,7 +12526,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E361" s="1"/>
+      <c r="E361" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
+        <v>2824.96</v>
+      </c>
       <c r="F361" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12482,7 +12560,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E362" s="1"/>
+      <c r="E362" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
+        <v>3969.19</v>
+      </c>
       <c r="F362" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12513,7 +12594,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E363" s="1"/>
+      <c r="E363" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
+        <v>4064.6</v>
+      </c>
       <c r="F363" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12544,7 +12628,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E364" s="1"/>
+      <c r="E364" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
+        <v>2356.85</v>
+      </c>
       <c r="F364" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12575,7 +12662,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E365" s="1"/>
+      <c r="E365" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
+        <v>2287.03</v>
+      </c>
       <c r="F365" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -12606,7 +12696,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E366" s="1"/>
+      <c r="E366" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
+        <v>2757.4</v>
+      </c>
       <c r="F366" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -11918,17 +11918,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
         <v>2356.85</v>
       </c>
-      <c r="F343" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G343" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H343" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F343" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2690.5)</f>
+        <v>2690.5</v>
+      </c>
+      <c r="G343" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.0)</f>
+        <v>62</v>
+      </c>
+      <c r="H343" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.395161290322584)</f>
+        <v>43.39516129</v>
       </c>
     </row>
     <row r="344">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -11952,17 +11952,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
         <v>2287.03</v>
       </c>
-      <c r="F344" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G344" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H344" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F344" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3328.5)</f>
+        <v>3328.5</v>
+      </c>
+      <c r="G344" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.0)</f>
+        <v>64</v>
+      </c>
+      <c r="H344" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0078125)</f>
+        <v>52.0078125</v>
       </c>
     </row>
     <row r="345">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -11986,17 +11986,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
         <v>2757.4</v>
       </c>
-      <c r="F345" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G345" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H345" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F345" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2934.01)</f>
+        <v>2934.01</v>
+      </c>
+      <c r="G345" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
+        <v>63</v>
+      </c>
+      <c r="H345" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.57158730158731)</f>
+        <v>46.5715873</v>
       </c>
     </row>
     <row r="346">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12020,17 +12020,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
         <v>3129.21</v>
       </c>
-      <c r="F346" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G346" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H346" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F346" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2524.0)</f>
+        <v>2524</v>
+      </c>
+      <c r="G346" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.0)</f>
+        <v>47</v>
+      </c>
+      <c r="H346" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.702127659574465)</f>
+        <v>53.70212766</v>
       </c>
     </row>
     <row r="347">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12054,17 +12054,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
         <v>2824.96</v>
       </c>
-      <c r="F347" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G347" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H347" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F347" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2651.0)</f>
+        <v>2651</v>
+      </c>
+      <c r="G347" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
+        <v>70</v>
+      </c>
+      <c r="H347" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.871428571428574)</f>
+        <v>37.87142857</v>
       </c>
     </row>
     <row r="348">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12054,17 +12054,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
         <v>2824.96</v>
       </c>
-      <c r="F347" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G347" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H347" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F347" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2651.0)</f>
+        <v>2651</v>
+      </c>
+      <c r="G347" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
+        <v>70</v>
+      </c>
+      <c r="H347" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.871428571428574)</f>
+        <v>37.87142857</v>
       </c>
     </row>
     <row r="348">
@@ -12088,17 +12088,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
         <v>3969.19</v>
       </c>
-      <c r="F348" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G348" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H348" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F348" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4429.01)</f>
+        <v>4429.01</v>
+      </c>
+      <c r="G348" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),99.0)</f>
+        <v>99</v>
+      </c>
+      <c r="H348" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.73747474747475)</f>
+        <v>44.73747475</v>
       </c>
     </row>
     <row r="349">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12122,17 +12122,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
         <v>4064.6</v>
       </c>
-      <c r="F349" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G349" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H349" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F349" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2350.5)</f>
+        <v>2350.5</v>
+      </c>
+      <c r="G349" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
+      </c>
+      <c r="H349" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.96938775510204)</f>
+        <v>47.96938776</v>
       </c>
     </row>
     <row r="350">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12156,17 +12156,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
         <v>2356.85</v>
       </c>
-      <c r="F350" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G350" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H350" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F350" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1849.0)</f>
+        <v>1849</v>
+      </c>
+      <c r="G350" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
+        <v>38</v>
+      </c>
+      <c r="H350" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.6578947368421)</f>
+        <v>48.65789474</v>
       </c>
     </row>
     <row r="351">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12190,17 +12190,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
         <v>2287.03</v>
       </c>
-      <c r="F351" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G351" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H351" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F351" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1986.51)</f>
+        <v>1986.51</v>
+      </c>
+      <c r="G351" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
+      </c>
+      <c r="H351" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.54102040816326)</f>
+        <v>40.54102041</v>
       </c>
     </row>
     <row r="352">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12224,17 +12224,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
         <v>2757.4</v>
       </c>
-      <c r="F352" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G352" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H352" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F352" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1610.0)</f>
+        <v>1610</v>
+      </c>
+      <c r="G352" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
+        <v>38</v>
+      </c>
+      <c r="H352" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.36842105263158)</f>
+        <v>42.36842105</v>
       </c>
     </row>
     <row r="353">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12224,17 +12224,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
         <v>2757.4</v>
       </c>
-      <c r="F352" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G352" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H352" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F352" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1610.0)</f>
+        <v>1610</v>
+      </c>
+      <c r="G352" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
+        <v>38</v>
+      </c>
+      <c r="H352" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.36842105263158)</f>
+        <v>42.36842105</v>
       </c>
     </row>
     <row r="353">
@@ -12258,17 +12258,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
         <v>3129.21</v>
       </c>
-      <c r="F353" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G353" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H353" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F353" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2127.5)</f>
+        <v>2127.5</v>
+      </c>
+      <c r="G353" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.0)</f>
+        <v>44</v>
+      </c>
+      <c r="H353" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.35227272727273)</f>
+        <v>48.35227273</v>
       </c>
     </row>
     <row r="354">
@@ -12459,8 +12459,8 @@
         <v>1</v>
       </c>
       <c r="E359" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
-        <v>2757.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F359" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12697,8 +12697,8 @@
         <v>2</v>
       </c>
       <c r="E366" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
-        <v>2757.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F366" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12258,17 +12258,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
         <v>3129.21</v>
       </c>
-      <c r="F353" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G353" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H353" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F353" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2127.5)</f>
+        <v>2127.5</v>
+      </c>
+      <c r="G353" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.0)</f>
+        <v>44</v>
+      </c>
+      <c r="H353" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.35227272727273)</f>
+        <v>48.35227273</v>
       </c>
     </row>
     <row r="354">
@@ -12459,8 +12459,8 @@
         <v>1</v>
       </c>
       <c r="E359" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
-        <v>2757.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F359" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12697,8 +12697,8 @@
         <v>2</v>
       </c>
       <c r="E366" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
-        <v>2757.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F366" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12292,17 +12292,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
         <v>2824.96</v>
       </c>
-      <c r="F354" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G354" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H354" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F354" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1266.0)</f>
+        <v>1266</v>
+      </c>
+      <c r="G354" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
+        <v>33</v>
+      </c>
+      <c r="H354" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.36363636363637)</f>
+        <v>38.36363636</v>
       </c>
     </row>
     <row r="355">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12326,17 +12326,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
         <v>3969.19</v>
       </c>
-      <c r="F355" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G355" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H355" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F355" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3372.0)</f>
+        <v>3372</v>
+      </c>
+      <c r="G355" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
+      </c>
+      <c r="H355" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.09090909090909)</f>
+        <v>51.09090909</v>
       </c>
     </row>
     <row r="356">
@@ -12360,17 +12360,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
         <v>4064.6</v>
       </c>
-      <c r="F356" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G356" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H356" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F356" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2802.5)</f>
+        <v>2802.5</v>
+      </c>
+      <c r="G356" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
+        <v>70</v>
+      </c>
+      <c r="H356" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.035714285714285)</f>
+        <v>40.03571429</v>
       </c>
     </row>
     <row r="357">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12394,17 +12394,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
         <v>2356.85</v>
       </c>
-      <c r="F357" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G357" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H357" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F357" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2690.5)</f>
+        <v>2690.5</v>
+      </c>
+      <c r="G357" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.0)</f>
+        <v>62</v>
+      </c>
+      <c r="H357" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.395161290322584)</f>
+        <v>43.39516129</v>
       </c>
     </row>
     <row r="358">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12428,17 +12428,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
         <v>2287.03</v>
       </c>
-      <c r="F358" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G358" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H358" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F358" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1277.02)</f>
+        <v>1277.02</v>
+      </c>
+      <c r="G358" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
+        <v>39</v>
+      </c>
+      <c r="H358" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.74410256410256)</f>
+        <v>32.74410256</v>
       </c>
     </row>
     <row r="359">
@@ -12496,17 +12496,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
         <v>3129.21</v>
       </c>
-      <c r="F360" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G360" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H360" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F360" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),941.02)</f>
+        <v>941.02</v>
+      </c>
+      <c r="G360" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.0)</f>
+        <v>31</v>
+      </c>
+      <c r="H360" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.355483870967742)</f>
+        <v>30.35548387</v>
       </c>
     </row>
     <row r="361">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12530,17 +12530,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
         <v>2824.96</v>
       </c>
-      <c r="F361" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G361" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H361" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F361" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1994.01)</f>
+        <v>1994.01</v>
+      </c>
+      <c r="G361" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
+        <v>52</v>
+      </c>
+      <c r="H361" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.346346153846156)</f>
+        <v>38.34634615</v>
       </c>
     </row>
     <row r="362">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12462,13 +12462,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="F359" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G359" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+      <c r="F359" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="G359" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H359" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12463,16 +12463,16 @@
         <v>0</v>
       </c>
       <c r="F359" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.01)</f>
+        <v>0.01</v>
       </c>
       <c r="G359" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="H359" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="H359" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.01)</f>
+        <v>0.01</v>
       </c>
     </row>
     <row r="360">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12564,17 +12564,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
         <v>3969.19</v>
       </c>
-      <c r="F362" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G362" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H362" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F362" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2806.51)</f>
+        <v>2806.51</v>
+      </c>
+      <c r="G362" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68.0)</f>
+        <v>68</v>
+      </c>
+      <c r="H362" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),41.27220588235294)</f>
+        <v>41.27220588</v>
       </c>
     </row>
     <row r="363">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12598,17 +12598,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
         <v>4064.6</v>
       </c>
-      <c r="F363" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G363" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H363" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F363" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3695.5)</f>
+        <v>3695.5</v>
+      </c>
+      <c r="G363" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
+      </c>
+      <c r="H363" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.623456790123456)</f>
+        <v>45.62345679</v>
       </c>
     </row>
     <row r="364">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12632,17 +12632,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
         <v>2356.85</v>
       </c>
-      <c r="F364" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G364" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H364" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F364" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3029.0)</f>
+        <v>3029</v>
+      </c>
+      <c r="G364" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69.0)</f>
+        <v>69</v>
+      </c>
+      <c r="H364" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.89855072463768)</f>
+        <v>43.89855072</v>
       </c>
     </row>
     <row r="365">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12327,16 +12327,16 @@
         <v>3969.19</v>
       </c>
       <c r="F355" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3372.0)</f>
-        <v>3372</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3522.0)</f>
+        <v>3522</v>
       </c>
       <c r="G355" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
         <v>66</v>
       </c>
       <c r="H355" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.09090909090909)</f>
-        <v>51.09090909</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.36363636363637)</f>
+        <v>53.36363636</v>
       </c>
     </row>
     <row r="356">
@@ -12666,17 +12666,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
         <v>2287.03</v>
       </c>
-      <c r="F365" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G365" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H365" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F365" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2334.51)</f>
+        <v>2334.51</v>
+      </c>
+      <c r="G365" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
+        <v>57</v>
+      </c>
+      <c r="H365" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.956315789473685)</f>
+        <v>40.95631579</v>
       </c>
     </row>
     <row r="366">
@@ -12700,17 +12700,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="F366" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G366" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H366" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F366" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.01)</f>
+        <v>0.01</v>
+      </c>
+      <c r="G366" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="H366" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.01)</f>
+        <v>0.01</v>
       </c>
     </row>
     <row r="367">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12714,35 +12714,53 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1"/>
-      <c r="B367" s="1"/>
+      <c r="A367" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B367" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
       <c r="C367" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D367" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D367" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E367" s="1"/>
-      <c r="F367" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G367" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H367" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F367" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2674.0)</f>
+        <v>2674</v>
+      </c>
+      <c r="G367" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="H367" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.48)</f>
+        <v>53.48</v>
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1"/>
-      <c r="B368" s="1"/>
+      <c r="A368" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B368" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46024.0)</f>
+        <v>46024</v>
+      </c>
       <c r="C368" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D368" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D368" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E368" s="1"/>
       <c r="F368" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12758,13 +12776,22 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1"/>
-      <c r="B369" s="1"/>
+      <c r="A369" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B369" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46025.0)</f>
+        <v>46025</v>
+      </c>
       <c r="C369" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D369" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D369" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E369" s="1"/>
       <c r="F369" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12780,13 +12807,22 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1"/>
-      <c r="B370" s="1"/>
+      <c r="A370" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B370" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46026.0)</f>
+        <v>46026</v>
+      </c>
       <c r="C370" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D370" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D370" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E370" s="1"/>
       <c r="F370" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12802,13 +12838,22 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1"/>
-      <c r="B371" s="1"/>
+      <c r="A371" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B371" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46027.0)</f>
+        <v>46027</v>
+      </c>
       <c r="C371" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D371" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D371" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E371" s="1"/>
       <c r="F371" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12824,13 +12869,22 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1"/>
-      <c r="B372" s="1"/>
+      <c r="A372" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B372" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46028.0)</f>
+        <v>46028</v>
+      </c>
       <c r="C372" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D372" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D372" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E372" s="1"/>
       <c r="F372" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12846,13 +12900,22 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1"/>
-      <c r="B373" s="1"/>
+      <c r="A373" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B373" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46029.0)</f>
+        <v>46029</v>
+      </c>
       <c r="C373" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D373" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D373" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E373" s="1"/>
       <c r="F373" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12868,13 +12931,22 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1"/>
-      <c r="B374" s="1"/>
+      <c r="A374" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B374" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46030.0)</f>
+        <v>46030</v>
+      </c>
       <c r="C374" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D374" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D374" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E374" s="1"/>
       <c r="F374" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12890,13 +12962,22 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1"/>
-      <c r="B375" s="1"/>
+      <c r="A375" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B375" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46031.0)</f>
+        <v>46031</v>
+      </c>
       <c r="C375" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D375" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D375" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E375" s="1"/>
       <c r="F375" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12912,13 +12993,22 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1"/>
-      <c r="B376" s="1"/>
+      <c r="A376" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B376" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
+        <v>46032</v>
+      </c>
       <c r="C376" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D376" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D376" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E376" s="1"/>
       <c r="F376" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12934,13 +13024,22 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1"/>
-      <c r="B377" s="1"/>
+      <c r="A377" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B377" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46033.0)</f>
+        <v>46033</v>
+      </c>
       <c r="C377" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D377" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D377" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E377" s="1"/>
       <c r="F377" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12956,13 +13055,22 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1"/>
-      <c r="B378" s="1"/>
+      <c r="A378" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B378" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
+        <v>46034</v>
+      </c>
       <c r="C378" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D378" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D378" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E378" s="1"/>
       <c r="F378" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12978,13 +13086,22 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1"/>
-      <c r="B379" s="1"/>
+      <c r="A379" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B379" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46035.0)</f>
+        <v>46035</v>
+      </c>
       <c r="C379" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D379" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D379" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E379" s="1"/>
       <c r="F379" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13000,13 +13117,22 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1"/>
-      <c r="B380" s="1"/>
+      <c r="A380" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B380" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46036.0)</f>
+        <v>46036</v>
+      </c>
       <c r="C380" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D380" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D380" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E380" s="1"/>
       <c r="F380" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13022,13 +13148,22 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1"/>
-      <c r="B381" s="1"/>
+      <c r="A381" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B381" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46037.0)</f>
+        <v>46037</v>
+      </c>
       <c r="C381" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D381" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D381" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E381" s="1"/>
       <c r="F381" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13044,13 +13179,22 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1"/>
-      <c r="B382" s="1"/>
+      <c r="A382" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B382" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46038.0)</f>
+        <v>46038</v>
+      </c>
       <c r="C382" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D382" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D382" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E382" s="1"/>
       <c r="F382" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13066,13 +13210,22 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1"/>
-      <c r="B383" s="1"/>
+      <c r="A383" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B383" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46039.0)</f>
+        <v>46039</v>
+      </c>
       <c r="C383" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D383" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D383" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E383" s="1"/>
       <c r="F383" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13088,13 +13241,22 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1"/>
-      <c r="B384" s="1"/>
+      <c r="A384" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B384" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46040.0)</f>
+        <v>46040</v>
+      </c>
       <c r="C384" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D384" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D384" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E384" s="1"/>
       <c r="F384" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13110,13 +13272,22 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1"/>
-      <c r="B385" s="1"/>
+      <c r="A385" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B385" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46041.0)</f>
+        <v>46041</v>
+      </c>
       <c r="C385" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D385" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D385" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E385" s="1"/>
       <c r="F385" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13132,13 +13303,22 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1"/>
-      <c r="B386" s="1"/>
+      <c r="A386" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B386" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
       <c r="C386" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D386" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D386" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E386" s="1"/>
       <c r="F386" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13154,13 +13334,22 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1"/>
-      <c r="B387" s="1"/>
+      <c r="A387" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B387" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
+        <v>46043</v>
+      </c>
       <c r="C387" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D387" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D387" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E387" s="1"/>
       <c r="F387" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13176,13 +13365,22 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1"/>
-      <c r="B388" s="1"/>
+      <c r="A388" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B388" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46044.0)</f>
+        <v>46044</v>
+      </c>
       <c r="C388" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D388" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D388" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E388" s="1"/>
       <c r="F388" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13198,13 +13396,22 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1"/>
-      <c r="B389" s="1"/>
+      <c r="A389" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B389" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46045.0)</f>
+        <v>46045</v>
+      </c>
       <c r="C389" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D389" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D389" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E389" s="1"/>
       <c r="F389" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13220,13 +13427,22 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1"/>
-      <c r="B390" s="1"/>
+      <c r="A390" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B390" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46046.0)</f>
+        <v>46046</v>
+      </c>
       <c r="C390" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D390" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D390" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E390" s="1"/>
       <c r="F390" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13242,13 +13458,22 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1"/>
-      <c r="B391" s="1"/>
+      <c r="A391" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B391" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46047.0)</f>
+        <v>46047</v>
+      </c>
       <c r="C391" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D391" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D391" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E391" s="1"/>
       <c r="F391" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13264,13 +13489,22 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1"/>
-      <c r="B392" s="1"/>
+      <c r="A392" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B392" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46048.0)</f>
+        <v>46048</v>
+      </c>
       <c r="C392" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D392" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D392" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E392" s="1"/>
       <c r="F392" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13286,13 +13520,22 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1"/>
-      <c r="B393" s="1"/>
+      <c r="A393" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B393" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46049.0)</f>
+        <v>46049</v>
+      </c>
       <c r="C393" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D393" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D393" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E393" s="1"/>
       <c r="F393" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13308,13 +13551,22 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1"/>
-      <c r="B394" s="1"/>
+      <c r="A394" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B394" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46050.0)</f>
+        <v>46050</v>
+      </c>
       <c r="C394" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D394" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D394" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E394" s="1"/>
       <c r="F394" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13330,13 +13582,22 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1"/>
-      <c r="B395" s="1"/>
+      <c r="A395" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B395" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46051.0)</f>
+        <v>46051</v>
+      </c>
       <c r="C395" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D395" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D395" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E395" s="1"/>
       <c r="F395" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13352,13 +13613,22 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1"/>
-      <c r="B396" s="1"/>
+      <c r="A396" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B396" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46052.0)</f>
+        <v>46052</v>
+      </c>
       <c r="C396" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D396" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D396" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E396" s="1"/>
       <c r="F396" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13374,13 +13644,22 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1"/>
-      <c r="B397" s="1"/>
+      <c r="A397" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B397" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46053.0)</f>
+        <v>46053</v>
+      </c>
       <c r="C397" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D397" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D397" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E397" s="1"/>
       <c r="F397" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12714,101 +12714,146 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1"/>
-      <c r="B367" s="1"/>
+      <c r="A367" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B367" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
       <c r="C367" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D367" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D367" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E367" s="1"/>
-      <c r="F367" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G367" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H367" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F367" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2674.0)</f>
+        <v>2674</v>
+      </c>
+      <c r="G367" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="H367" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.48)</f>
+        <v>53.48</v>
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1"/>
-      <c r="B368" s="1"/>
+      <c r="A368" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B368" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46024.0)</f>
+        <v>46024</v>
+      </c>
       <c r="C368" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D368" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D368" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E368" s="1"/>
-      <c r="F368" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G368" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H368" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F368" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4655.5)</f>
+        <v>4655.5</v>
+      </c>
+      <c r="G368" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.0)</f>
+        <v>78</v>
+      </c>
+      <c r="H368" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.68589743589744)</f>
+        <v>59.68589744</v>
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1"/>
-      <c r="B369" s="1"/>
+      <c r="A369" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B369" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46025.0)</f>
+        <v>46025</v>
+      </c>
       <c r="C369" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D369" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D369" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E369" s="1"/>
-      <c r="F369" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G369" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H369" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F369" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5409.5)</f>
+        <v>5409.5</v>
+      </c>
+      <c r="G369" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),121.0)</f>
+        <v>121</v>
+      </c>
+      <c r="H369" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.70661157024794)</f>
+        <v>44.70661157</v>
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1"/>
-      <c r="B370" s="1"/>
+      <c r="A370" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B370" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46026.0)</f>
+        <v>46026</v>
+      </c>
       <c r="C370" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D370" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D370" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E370" s="1"/>
-      <c r="F370" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G370" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H370" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F370" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5360.01)</f>
+        <v>5360.01</v>
+      </c>
+      <c r="G370" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
+      </c>
+      <c r="H370" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.72736363636364)</f>
+        <v>48.72736364</v>
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1"/>
-      <c r="B371" s="1"/>
+      <c r="A371" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B371" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46027.0)</f>
+        <v>46027</v>
+      </c>
       <c r="C371" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D371" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D371" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E371" s="1"/>
       <c r="F371" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12824,13 +12869,22 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1"/>
-      <c r="B372" s="1"/>
+      <c r="A372" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B372" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46028.0)</f>
+        <v>46028</v>
+      </c>
       <c r="C372" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D372" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D372" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E372" s="1"/>
       <c r="F372" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12846,13 +12900,22 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1"/>
-      <c r="B373" s="1"/>
+      <c r="A373" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B373" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46029.0)</f>
+        <v>46029</v>
+      </c>
       <c r="C373" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D373" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D373" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E373" s="1"/>
       <c r="F373" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12868,13 +12931,22 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1"/>
-      <c r="B374" s="1"/>
+      <c r="A374" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B374" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46030.0)</f>
+        <v>46030</v>
+      </c>
       <c r="C374" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D374" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D374" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E374" s="1"/>
       <c r="F374" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12890,13 +12962,22 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1"/>
-      <c r="B375" s="1"/>
+      <c r="A375" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B375" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46031.0)</f>
+        <v>46031</v>
+      </c>
       <c r="C375" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D375" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D375" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E375" s="1"/>
       <c r="F375" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12912,13 +12993,22 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1"/>
-      <c r="B376" s="1"/>
+      <c r="A376" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B376" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
+        <v>46032</v>
+      </c>
       <c r="C376" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D376" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D376" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E376" s="1"/>
       <c r="F376" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12934,13 +13024,22 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1"/>
-      <c r="B377" s="1"/>
+      <c r="A377" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B377" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46033.0)</f>
+        <v>46033</v>
+      </c>
       <c r="C377" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D377" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D377" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E377" s="1"/>
       <c r="F377" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12956,13 +13055,22 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1"/>
-      <c r="B378" s="1"/>
+      <c r="A378" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B378" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
+        <v>46034</v>
+      </c>
       <c r="C378" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D378" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D378" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E378" s="1"/>
       <c r="F378" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -12978,13 +13086,22 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1"/>
-      <c r="B379" s="1"/>
+      <c r="A379" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B379" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46035.0)</f>
+        <v>46035</v>
+      </c>
       <c r="C379" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D379" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D379" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E379" s="1"/>
       <c r="F379" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13000,13 +13117,22 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1"/>
-      <c r="B380" s="1"/>
+      <c r="A380" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B380" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46036.0)</f>
+        <v>46036</v>
+      </c>
       <c r="C380" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D380" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D380" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E380" s="1"/>
       <c r="F380" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13022,13 +13148,22 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1"/>
-      <c r="B381" s="1"/>
+      <c r="A381" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B381" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46037.0)</f>
+        <v>46037</v>
+      </c>
       <c r="C381" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D381" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D381" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E381" s="1"/>
       <c r="F381" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13044,13 +13179,22 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1"/>
-      <c r="B382" s="1"/>
+      <c r="A382" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B382" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46038.0)</f>
+        <v>46038</v>
+      </c>
       <c r="C382" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D382" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D382" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E382" s="1"/>
       <c r="F382" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13066,13 +13210,22 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1"/>
-      <c r="B383" s="1"/>
+      <c r="A383" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B383" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46039.0)</f>
+        <v>46039</v>
+      </c>
       <c r="C383" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D383" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D383" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E383" s="1"/>
       <c r="F383" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13088,13 +13241,22 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1"/>
-      <c r="B384" s="1"/>
+      <c r="A384" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B384" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46040.0)</f>
+        <v>46040</v>
+      </c>
       <c r="C384" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D384" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D384" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E384" s="1"/>
       <c r="F384" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13110,13 +13272,22 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1"/>
-      <c r="B385" s="1"/>
+      <c r="A385" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B385" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46041.0)</f>
+        <v>46041</v>
+      </c>
       <c r="C385" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D385" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D385" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E385" s="1"/>
       <c r="F385" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13132,13 +13303,22 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1"/>
-      <c r="B386" s="1"/>
+      <c r="A386" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B386" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
       <c r="C386" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D386" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D386" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E386" s="1"/>
       <c r="F386" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13154,13 +13334,22 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1"/>
-      <c r="B387" s="1"/>
+      <c r="A387" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B387" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
+        <v>46043</v>
+      </c>
       <c r="C387" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D387" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D387" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E387" s="1"/>
       <c r="F387" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13176,13 +13365,22 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1"/>
-      <c r="B388" s="1"/>
+      <c r="A388" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B388" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46044.0)</f>
+        <v>46044</v>
+      </c>
       <c r="C388" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D388" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D388" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E388" s="1"/>
       <c r="F388" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13198,13 +13396,22 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1"/>
-      <c r="B389" s="1"/>
+      <c r="A389" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B389" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46045.0)</f>
+        <v>46045</v>
+      </c>
       <c r="C389" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D389" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D389" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E389" s="1"/>
       <c r="F389" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13220,13 +13427,22 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1"/>
-      <c r="B390" s="1"/>
+      <c r="A390" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B390" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46046.0)</f>
+        <v>46046</v>
+      </c>
       <c r="C390" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D390" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D390" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E390" s="1"/>
       <c r="F390" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13242,13 +13458,22 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1"/>
-      <c r="B391" s="1"/>
+      <c r="A391" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B391" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46047.0)</f>
+        <v>46047</v>
+      </c>
       <c r="C391" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D391" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D391" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E391" s="1"/>
       <c r="F391" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13264,13 +13489,22 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1"/>
-      <c r="B392" s="1"/>
+      <c r="A392" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B392" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46048.0)</f>
+        <v>46048</v>
+      </c>
       <c r="C392" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D392" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D392" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E392" s="1"/>
       <c r="F392" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13286,13 +13520,22 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1"/>
-      <c r="B393" s="1"/>
+      <c r="A393" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B393" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46049.0)</f>
+        <v>46049</v>
+      </c>
       <c r="C393" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D393" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D393" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E393" s="1"/>
       <c r="F393" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13308,13 +13551,22 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1"/>
-      <c r="B394" s="1"/>
+      <c r="A394" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B394" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46050.0)</f>
+        <v>46050</v>
+      </c>
       <c r="C394" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D394" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D394" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E394" s="1"/>
       <c r="F394" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13330,13 +13582,22 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1"/>
-      <c r="B395" s="1"/>
+      <c r="A395" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B395" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46051.0)</f>
+        <v>46051</v>
+      </c>
       <c r="C395" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D395" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D395" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E395" s="1"/>
       <c r="F395" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13352,13 +13613,22 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1"/>
-      <c r="B396" s="1"/>
+      <c r="A396" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B396" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46052.0)</f>
+        <v>46052</v>
+      </c>
       <c r="C396" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D396" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D396" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E396" s="1"/>
       <c r="F396" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13374,13 +13644,22 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1"/>
-      <c r="B397" s="1"/>
+      <c r="A397" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
+      </c>
+      <c r="B397" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46053.0)</f>
+        <v>46053</v>
+      </c>
       <c r="C397" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D397" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D397" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E397" s="1"/>
       <c r="F397" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12855,17 +12855,17 @@
         <v>1</v>
       </c>
       <c r="E371" s="1"/>
-      <c r="F371" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G371" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H371" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F371" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2465.0)</f>
+        <v>2465</v>
+      </c>
+      <c r="G371" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
+        <v>56</v>
+      </c>
+      <c r="H371" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.017857142857146)</f>
+        <v>44.01785714</v>
       </c>
     </row>
     <row r="372">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12855,17 +12855,17 @@
         <v>1</v>
       </c>
       <c r="E371" s="1"/>
-      <c r="F371" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G371" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H371" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F371" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2465.0)</f>
+        <v>2465</v>
+      </c>
+      <c r="G371" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
+        <v>56</v>
+      </c>
+      <c r="H371" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.017857142857146)</f>
+        <v>44.01785714</v>
       </c>
     </row>
     <row r="372">
@@ -12886,17 +12886,17 @@
         <v>2</v>
       </c>
       <c r="E372" s="1"/>
-      <c r="F372" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G372" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H372" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F372" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2457.51)</f>
+        <v>2457.51</v>
+      </c>
+      <c r="G372" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
+        <v>56</v>
+      </c>
+      <c r="H372" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.88410714285715)</f>
+        <v>43.88410714</v>
       </c>
     </row>
     <row r="373">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12917,17 +12917,17 @@
         <v>1</v>
       </c>
       <c r="E373" s="1"/>
-      <c r="F373" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G373" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H373" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F373" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3659.0)</f>
+        <v>3659</v>
+      </c>
+      <c r="G373" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),79.0)</f>
+        <v>79</v>
+      </c>
+      <c r="H373" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.31645569620253)</f>
+        <v>46.3164557</v>
       </c>
     </row>
     <row r="374">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12948,17 +12948,17 @@
         <v>2</v>
       </c>
       <c r="E374" s="1"/>
-      <c r="F374" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G374" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H374" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F374" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2701.5)</f>
+        <v>2701.5</v>
+      </c>
+      <c r="G374" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
+        <v>57</v>
+      </c>
+      <c r="H374" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.39473684210526)</f>
+        <v>47.39473684</v>
       </c>
     </row>
     <row r="375">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12979,17 +12979,17 @@
         <v>1</v>
       </c>
       <c r="E375" s="1"/>
-      <c r="F375" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G375" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H375" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F375" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3397.5)</f>
+        <v>3397.5</v>
+      </c>
+      <c r="G375" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),79.0)</f>
+        <v>79</v>
+      </c>
+      <c r="H375" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.00632911392405)</f>
+        <v>43.00632911</v>
       </c>
     </row>
     <row r="376">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12979,17 +12979,17 @@
         <v>1</v>
       </c>
       <c r="E375" s="1"/>
-      <c r="F375" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G375" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H375" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F375" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3397.5)</f>
+        <v>3397.5</v>
+      </c>
+      <c r="G375" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),79.0)</f>
+        <v>79</v>
+      </c>
+      <c r="H375" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.00632911392405)</f>
+        <v>43.00632911</v>
       </c>
     </row>
     <row r="376">
@@ -13010,17 +13010,17 @@
         <v>2</v>
       </c>
       <c r="E376" s="1"/>
-      <c r="F376" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G376" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H376" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F376" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5844.01)</f>
+        <v>5844.01</v>
+      </c>
+      <c r="G376" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
+        <v>117</v>
+      </c>
+      <c r="H376" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.94880341880342)</f>
+        <v>49.94880342</v>
       </c>
     </row>
     <row r="377">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13041,17 +13041,17 @@
         <v>1</v>
       </c>
       <c r="E377" s="1"/>
-      <c r="F377" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G377" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H377" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F377" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5247.0)</f>
+        <v>5247</v>
+      </c>
+      <c r="G377" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
+        <v>98</v>
+      </c>
+      <c r="H377" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.54081632653061)</f>
+        <v>53.54081633</v>
       </c>
     </row>
     <row r="378">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13072,17 +13072,17 @@
         <v>2</v>
       </c>
       <c r="E378" s="1"/>
-      <c r="F378" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G378" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H378" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F378" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2547.5)</f>
+        <v>2547.5</v>
+      </c>
+      <c r="G378" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.0)</f>
+        <v>62</v>
+      </c>
+      <c r="H378" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),41.08870967741935)</f>
+        <v>41.08870968</v>
       </c>
     </row>
     <row r="379">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -69,6 +69,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13103,17 +13107,17 @@
         <v>1</v>
       </c>
       <c r="E379" s="1"/>
-      <c r="F379" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G379" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H379" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F379" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1989.0)</f>
+        <v>1989</v>
+      </c>
+      <c r="G379" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.0)</f>
+        <v>47</v>
+      </c>
+      <c r="H379" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.319148936170215)</f>
+        <v>42.31914894</v>
       </c>
     </row>
     <row r="380">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13138,17 +13138,17 @@
         <v>2</v>
       </c>
       <c r="E380" s="1"/>
-      <c r="F380" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G380" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H380" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F380" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3473.04)</f>
+        <v>3473.04</v>
+      </c>
+      <c r="G380" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68.0)</f>
+        <v>68</v>
+      </c>
+      <c r="H380" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.07411764705882)</f>
+        <v>51.07411765</v>
       </c>
     </row>
     <row r="381">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -12734,7 +12734,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E367" s="1"/>
+      <c r="E367" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
+        <v>3129.21</v>
+      </c>
       <c r="F367" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2674.0)</f>
         <v>2674</v>
@@ -12765,7 +12768,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E368" s="1"/>
+      <c r="E368" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
+        <v>2824.96</v>
+      </c>
       <c r="F368" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4655.5)</f>
         <v>4655.5</v>
@@ -12796,7 +12802,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E369" s="1"/>
+      <c r="E369" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
+        <v>3969.19</v>
+      </c>
       <c r="F369" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5409.5)</f>
         <v>5409.5</v>
@@ -12827,7 +12836,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E370" s="1"/>
+      <c r="E370" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
+        <v>4064.6</v>
+      </c>
       <c r="F370" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5360.01)</f>
         <v>5360.01</v>
@@ -12858,7 +12870,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E371" s="1"/>
+      <c r="E371" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
+        <v>2356.85</v>
+      </c>
       <c r="F371" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2465.0)</f>
         <v>2465</v>
@@ -12889,7 +12904,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E372" s="1"/>
+      <c r="E372" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
+        <v>2287.03</v>
+      </c>
       <c r="F372" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2457.51)</f>
         <v>2457.51</v>
@@ -12920,7 +12938,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E373" s="1"/>
+      <c r="E373" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
+        <v>2757.4</v>
+      </c>
       <c r="F373" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3659.0)</f>
         <v>3659</v>
@@ -12951,7 +12972,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E374" s="1"/>
+      <c r="E374" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
+        <v>3129.21</v>
+      </c>
       <c r="F374" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2701.5)</f>
         <v>2701.5</v>
@@ -12982,7 +13006,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E375" s="1"/>
+      <c r="E375" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
+        <v>2824.96</v>
+      </c>
       <c r="F375" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3397.5)</f>
         <v>3397.5</v>
@@ -13013,7 +13040,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E376" s="1"/>
+      <c r="E376" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
+        <v>3969.19</v>
+      </c>
       <c r="F376" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5844.01)</f>
         <v>5844.01</v>
@@ -13044,7 +13074,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E377" s="1"/>
+      <c r="E377" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
+        <v>4064.6</v>
+      </c>
       <c r="F377" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5247.0)</f>
         <v>5247</v>
@@ -13075,7 +13108,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E378" s="1"/>
+      <c r="E378" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
+        <v>2356.85</v>
+      </c>
       <c r="F378" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2547.5)</f>
         <v>2547.5</v>
@@ -13106,7 +13142,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E379" s="1"/>
+      <c r="E379" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
+        <v>2287.03</v>
+      </c>
       <c r="F379" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1989.0)</f>
         <v>1989</v>
@@ -13137,7 +13176,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E380" s="1"/>
+      <c r="E380" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
+        <v>2757.4</v>
+      </c>
       <c r="F380" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3473.04)</f>
         <v>3473.04</v>
@@ -13168,7 +13210,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E381" s="1"/>
+      <c r="E381" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
+        <v>3129.21</v>
+      </c>
       <c r="F381" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13199,7 +13244,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E382" s="1"/>
+      <c r="E382" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
+        <v>2824.96</v>
+      </c>
       <c r="F382" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13230,7 +13278,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E383" s="1"/>
+      <c r="E383" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
+        <v>3969.19</v>
+      </c>
       <c r="F383" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13261,7 +13312,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E384" s="1"/>
+      <c r="E384" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
+        <v>4064.6</v>
+      </c>
       <c r="F384" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13292,7 +13346,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E385" s="1"/>
+      <c r="E385" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
+        <v>2356.85</v>
+      </c>
       <c r="F385" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13323,7 +13380,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E386" s="1"/>
+      <c r="E386" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
+        <v>2287.03</v>
+      </c>
       <c r="F386" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13354,7 +13414,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E387" s="1"/>
+      <c r="E387" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
+        <v>2757.4</v>
+      </c>
       <c r="F387" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13385,7 +13448,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E388" s="1"/>
+      <c r="E388" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
+        <v>3129.21</v>
+      </c>
       <c r="F388" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13416,7 +13482,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E389" s="1"/>
+      <c r="E389" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
+        <v>2824.96</v>
+      </c>
       <c r="F389" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13447,7 +13516,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E390" s="1"/>
+      <c r="E390" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
+        <v>3969.19</v>
+      </c>
       <c r="F390" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13478,7 +13550,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E391" s="1"/>
+      <c r="E391" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
+        <v>4064.6</v>
+      </c>
       <c r="F391" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13509,7 +13584,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E392" s="1"/>
+      <c r="E392" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
+        <v>2356.85</v>
+      </c>
       <c r="F392" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13540,7 +13618,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E393" s="1"/>
+      <c r="E393" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
+        <v>2287.03</v>
+      </c>
       <c r="F393" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13571,7 +13652,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E394" s="1"/>
+      <c r="E394" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
+        <v>2757.4</v>
+      </c>
       <c r="F394" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13602,7 +13686,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E395" s="1"/>
+      <c r="E395" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
+        <v>3129.21</v>
+      </c>
       <c r="F395" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13633,7 +13720,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E396" s="1"/>
+      <c r="E396" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
+        <v>2824.96</v>
+      </c>
       <c r="F396" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13664,7 +13754,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E397" s="1"/>
+      <c r="E397" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
+        <v>3969.19</v>
+      </c>
       <c r="F397" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13214,17 +13214,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
         <v>3129.21</v>
       </c>
-      <c r="F381" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G381" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H381" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F381" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2970.0)</f>
+        <v>2970</v>
+      </c>
+      <c r="G381" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
+      </c>
+      <c r="H381" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.68493150684932)</f>
+        <v>40.68493151</v>
       </c>
     </row>
     <row r="382">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13248,17 +13248,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
         <v>2824.96</v>
       </c>
-      <c r="F382" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G382" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H382" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F382" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3421.5)</f>
+        <v>3421.5</v>
+      </c>
+      <c r="G382" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.0)</f>
+        <v>84</v>
+      </c>
+      <c r="H382" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.732142857142854)</f>
+        <v>40.73214286</v>
       </c>
     </row>
     <row r="383">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13324,17 +13324,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
         <v>4064.6</v>
       </c>
-      <c r="F384" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G384" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H384" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F384" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6474.0)</f>
+        <v>6474</v>
+      </c>
+      <c r="G384" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
+      </c>
+      <c r="H384" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24285714285714)</f>
+        <v>46.24285714</v>
       </c>
     </row>
     <row r="385">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13358,17 +13358,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
         <v>2356.85</v>
       </c>
-      <c r="F385" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G385" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H385" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F385" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.51)</f>
+        <v>2201.51</v>
+      </c>
+      <c r="G385" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.0)</f>
+        <v>62</v>
+      </c>
+      <c r="H385" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.50822580645162)</f>
+        <v>35.50822581</v>
       </c>
     </row>
     <row r="386">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13392,17 +13392,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
         <v>2287.03</v>
       </c>
-      <c r="F386" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G386" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H386" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F386" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7027.02)</f>
+        <v>7027.02</v>
+      </c>
+      <c r="G386" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),167.0)</f>
+        <v>167</v>
+      </c>
+      <c r="H386" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.07796407185629)</f>
+        <v>42.07796407</v>
       </c>
     </row>
     <row r="387">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13392,17 +13392,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
         <v>2287.03</v>
       </c>
-      <c r="F386" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G386" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H386" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F386" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7027.02)</f>
+        <v>7027.02</v>
+      </c>
+      <c r="G386" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),167.0)</f>
+        <v>167</v>
+      </c>
+      <c r="H386" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.07796407185629)</f>
+        <v>42.07796407</v>
       </c>
     </row>
     <row r="387">
@@ -13426,17 +13426,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
         <v>2757.4</v>
       </c>
-      <c r="F387" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G387" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H387" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F387" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1784.0)</f>
+        <v>1784</v>
+      </c>
+      <c r="G387" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="H387" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.68)</f>
+        <v>35.68</v>
       </c>
     </row>
     <row r="388">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13426,17 +13426,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
         <v>2757.4</v>
       </c>
-      <c r="F387" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G387" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H387" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F387" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1784.0)</f>
+        <v>1784</v>
+      </c>
+      <c r="G387" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="H387" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.68)</f>
+        <v>35.68</v>
       </c>
     </row>
     <row r="388">
@@ -13460,17 +13460,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
         <v>3129.21</v>
       </c>
-      <c r="F388" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G388" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H388" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F388" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4027.53)</f>
+        <v>4027.53</v>
+      </c>
+      <c r="G388" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),67.0)</f>
+        <v>67</v>
+      </c>
+      <c r="H388" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.112388059701495)</f>
+        <v>60.11238806</v>
       </c>
     </row>
     <row r="389">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13494,17 +13494,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
         <v>2824.96</v>
       </c>
-      <c r="F389" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G389" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H389" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F389" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3482.0)</f>
+        <v>3482</v>
+      </c>
+      <c r="G389" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),151.0)</f>
+        <v>151</v>
+      </c>
+      <c r="H389" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.05960264900662)</f>
+        <v>23.05960265</v>
       </c>
     </row>
     <row r="390">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13528,17 +13528,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
         <v>3969.19</v>
       </c>
-      <c r="F390" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G390" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H390" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F390" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6372.0)</f>
+        <v>6372</v>
+      </c>
+      <c r="G390" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.0)</f>
+        <v>150</v>
+      </c>
+      <c r="H390" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.48)</f>
+        <v>42.48</v>
       </c>
     </row>
     <row r="391">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13562,17 +13562,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
         <v>4064.6</v>
       </c>
-      <c r="F391" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G391" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H391" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F391" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5614.5)</f>
+        <v>5614.5</v>
+      </c>
+      <c r="G391" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
+      </c>
+      <c r="H391" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.129464285714285)</f>
+        <v>50.12946429</v>
       </c>
     </row>
     <row r="392">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13562,17 +13562,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4064.6)</f>
         <v>4064.6</v>
       </c>
-      <c r="F391" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G391" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H391" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F391" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5614.5)</f>
+        <v>5614.5</v>
+      </c>
+      <c r="G391" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
+      </c>
+      <c r="H391" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.129464285714285)</f>
+        <v>50.12946429</v>
       </c>
     </row>
     <row r="392">
@@ -13596,17 +13596,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2356.85)</f>
         <v>2356.85</v>
       </c>
-      <c r="F392" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G392" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H392" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F392" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1805.0)</f>
+        <v>1805</v>
+      </c>
+      <c r="G392" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="H392" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.1)</f>
+        <v>36.1</v>
       </c>
     </row>
     <row r="393">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13630,17 +13630,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2287.03)</f>
         <v>2287.03</v>
       </c>
-      <c r="F393" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G393" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H393" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F393" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2564.0)</f>
+        <v>2564</v>
+      </c>
+      <c r="G393" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.0)</f>
+        <v>64</v>
+      </c>
+      <c r="H393" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0625)</f>
+        <v>40.0625</v>
       </c>
     </row>
     <row r="394">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13664,17 +13664,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2757.4)</f>
         <v>2757.4</v>
       </c>
-      <c r="F394" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G394" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H394" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F394" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4048.5)</f>
+        <v>4048.5</v>
+      </c>
+      <c r="G394" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),75.0)</f>
+        <v>75</v>
+      </c>
+      <c r="H394" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.98)</f>
+        <v>53.98</v>
       </c>
     </row>
     <row r="395">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13698,17 +13698,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3129.21)</f>
         <v>3129.21</v>
       </c>
-      <c r="F395" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G395" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H395" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F395" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3109.0)</f>
+        <v>3109</v>
+      </c>
+      <c r="G395" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
+        <v>70</v>
+      </c>
+      <c r="H395" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.41428571428571)</f>
+        <v>44.41428571</v>
       </c>
     </row>
     <row r="396">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13732,17 +13732,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2824.96)</f>
         <v>2824.96</v>
       </c>
-      <c r="F396" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G396" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H396" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F396" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2112.0)</f>
+        <v>2112</v>
+      </c>
+      <c r="G396" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="H396" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.24)</f>
+        <v>42.24</v>
       </c>
     </row>
     <row r="397">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13766,17 +13766,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3969.19)</f>
         <v>3969.19</v>
       </c>
-      <c r="F397" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G397" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H397" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F397" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4380.5)</f>
+        <v>4380.5</v>
+      </c>
+      <c r="G397" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
+        <v>98</v>
+      </c>
+      <c r="H397" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.69897959183673)</f>
+        <v>44.69897959</v>
       </c>
     </row>
     <row r="398">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13780,57 +13780,84 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="6"/>
-      <c r="B398" s="6"/>
+      <c r="A398" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B398" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
       <c r="C398" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D398" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D398" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E398" s="6"/>
-      <c r="F398" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G398" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H398" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F398" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6048.5)</f>
+        <v>6048.5</v>
+      </c>
+      <c r="G398" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
+      </c>
+      <c r="H398" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.004629629629626)</f>
+        <v>56.00462963</v>
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="6"/>
-      <c r="B399" s="6"/>
+      <c r="A399" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B399" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46055.0)</f>
+        <v>46055</v>
+      </c>
       <c r="C399" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D399" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D399" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E399" s="6"/>
-      <c r="F399" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G399" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H399" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F399" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2024.5)</f>
+        <v>2024.5</v>
+      </c>
+      <c r="G399" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.0)</f>
+        <v>47</v>
+      </c>
+      <c r="H399" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.07446808510638)</f>
+        <v>43.07446809</v>
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="6"/>
-      <c r="B400" s="6"/>
+      <c r="A400" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B400" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46056.0)</f>
+        <v>46056</v>
+      </c>
       <c r="C400" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D400" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D400" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E400" s="6"/>
       <c r="F400" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13846,13 +13873,22 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="6"/>
-      <c r="B401" s="6"/>
+      <c r="A401" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B401" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46057.0)</f>
+        <v>46057</v>
+      </c>
       <c r="C401" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D401" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D401" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E401" s="6"/>
       <c r="F401" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13868,13 +13904,22 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="6"/>
-      <c r="B402" s="6"/>
+      <c r="A402" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B402" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46058.0)</f>
+        <v>46058</v>
+      </c>
       <c r="C402" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D402" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D402" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E402" s="6"/>
       <c r="F402" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13890,13 +13935,22 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="6"/>
-      <c r="B403" s="6"/>
+      <c r="A403" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B403" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46059.0)</f>
+        <v>46059</v>
+      </c>
       <c r="C403" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D403" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D403" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E403" s="6"/>
       <c r="F403" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13912,13 +13966,22 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="6"/>
-      <c r="B404" s="6"/>
+      <c r="A404" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B404" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46060.0)</f>
+        <v>46060</v>
+      </c>
       <c r="C404" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D404" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D404" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E404" s="6"/>
       <c r="F404" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13934,13 +13997,22 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="6"/>
-      <c r="B405" s="6"/>
+      <c r="A405" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B405" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46061.0)</f>
+        <v>46061</v>
+      </c>
       <c r="C405" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D405" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D405" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E405" s="6"/>
       <c r="F405" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13956,13 +14028,22 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="6"/>
-      <c r="B406" s="6"/>
+      <c r="A406" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B406" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46062.0)</f>
+        <v>46062</v>
+      </c>
       <c r="C406" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D406" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D406" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E406" s="6"/>
       <c r="F406" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -13978,13 +14059,22 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="6"/>
-      <c r="B407" s="6"/>
+      <c r="A407" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B407" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46063.0)</f>
+        <v>46063</v>
+      </c>
       <c r="C407" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D407" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D407" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E407" s="6"/>
       <c r="F407" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14000,13 +14090,22 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="6"/>
-      <c r="B408" s="6"/>
+      <c r="A408" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B408" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46064.0)</f>
+        <v>46064</v>
+      </c>
       <c r="C408" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D408" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D408" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E408" s="6"/>
       <c r="F408" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14022,13 +14121,22 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="6"/>
-      <c r="B409" s="6"/>
+      <c r="A409" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B409" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46065.0)</f>
+        <v>46065</v>
+      </c>
       <c r="C409" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D409" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D409" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E409" s="6"/>
       <c r="F409" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14044,13 +14152,22 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="6"/>
-      <c r="B410" s="6"/>
+      <c r="A410" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B410" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46066.0)</f>
+        <v>46066</v>
+      </c>
       <c r="C410" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D410" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D410" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E410" s="6"/>
       <c r="F410" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14066,13 +14183,22 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="6"/>
-      <c r="B411" s="6"/>
+      <c r="A411" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B411" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46067.0)</f>
+        <v>46067</v>
+      </c>
       <c r="C411" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D411" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D411" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E411" s="6"/>
       <c r="F411" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14088,13 +14214,22 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="6"/>
-      <c r="B412" s="6"/>
+      <c r="A412" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B412" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46068.0)</f>
+        <v>46068</v>
+      </c>
       <c r="C412" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D412" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D412" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E412" s="6"/>
       <c r="F412" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14110,13 +14245,22 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="6"/>
-      <c r="B413" s="6"/>
+      <c r="A413" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B413" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46069.0)</f>
+        <v>46069</v>
+      </c>
       <c r="C413" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D413" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D413" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E413" s="6"/>
       <c r="F413" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14132,13 +14276,22 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="6"/>
-      <c r="B414" s="6"/>
+      <c r="A414" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B414" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46070.0)</f>
+        <v>46070</v>
+      </c>
       <c r="C414" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D414" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D414" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E414" s="6"/>
       <c r="F414" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14154,13 +14307,22 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="6"/>
-      <c r="B415" s="6"/>
+      <c r="A415" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B415" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46071.0)</f>
+        <v>46071</v>
+      </c>
       <c r="C415" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D415" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D415" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E415" s="6"/>
       <c r="F415" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14176,13 +14338,22 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="6"/>
-      <c r="B416" s="6"/>
+      <c r="A416" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B416" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46072.0)</f>
+        <v>46072</v>
+      </c>
       <c r="C416" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D416" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D416" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E416" s="6"/>
       <c r="F416" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14198,13 +14369,22 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="6"/>
-      <c r="B417" s="6"/>
+      <c r="A417" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B417" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46073.0)</f>
+        <v>46073</v>
+      </c>
       <c r="C417" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D417" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D417" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E417" s="6"/>
       <c r="F417" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14220,13 +14400,22 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="6"/>
-      <c r="B418" s="6"/>
+      <c r="A418" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B418" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46074.0)</f>
+        <v>46074</v>
+      </c>
       <c r="C418" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D418" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D418" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E418" s="6"/>
       <c r="F418" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14242,13 +14431,22 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="6"/>
-      <c r="B419" s="6"/>
+      <c r="A419" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B419" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46075.0)</f>
+        <v>46075</v>
+      </c>
       <c r="C419" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D419" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"domingo")</f>
+        <v>domingo</v>
+      </c>
+      <c r="D419" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E419" s="6"/>
       <c r="F419" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14264,13 +14462,22 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="6"/>
-      <c r="B420" s="6"/>
+      <c r="A420" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B420" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46076.0)</f>
+        <v>46076</v>
+      </c>
       <c r="C420" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D420" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"segunda-feira")</f>
+        <v>segunda-feira</v>
+      </c>
+      <c r="D420" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E420" s="6"/>
       <c r="F420" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14286,13 +14493,22 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="6"/>
-      <c r="B421" s="6"/>
+      <c r="A421" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B421" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46077.0)</f>
+        <v>46077</v>
+      </c>
       <c r="C421" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D421" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"terça-feira")</f>
+        <v>terça-feira</v>
+      </c>
+      <c r="D421" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E421" s="6"/>
       <c r="F421" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14308,13 +14524,22 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="6"/>
-      <c r="B422" s="6"/>
+      <c r="A422" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B422" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46078.0)</f>
+        <v>46078</v>
+      </c>
       <c r="C422" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D422" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quarta-feira")</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="D422" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E422" s="6"/>
       <c r="F422" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14330,13 +14555,22 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="6"/>
-      <c r="B423" s="6"/>
+      <c r="A423" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B423" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46079.0)</f>
+        <v>46079</v>
+      </c>
       <c r="C423" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D423" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"quinta-feira")</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="D423" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E423" s="6"/>
       <c r="F423" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14352,13 +14586,22 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="6"/>
-      <c r="B424" s="6"/>
+      <c r="A424" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B424" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46080.0)</f>
+        <v>46080</v>
+      </c>
       <c r="C424" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D424" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sexta-feira")</f>
+        <v>sexta-feira</v>
+      </c>
+      <c r="D424" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="E424" s="6"/>
       <c r="F424" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
@@ -14374,13 +14617,22 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="6"/>
-      <c r="B425" s="6"/>
+      <c r="A425" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
+      </c>
+      <c r="B425" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46081.0)</f>
+        <v>46081</v>
+      </c>
       <c r="C425" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="D425" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="D425" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="E425" s="6"/>
       <c r="F425" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13796,7 +13796,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E398" s="6"/>
+      <c r="E398" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4579.57)</f>
+        <v>4579.57</v>
+      </c>
       <c r="F398" s="7">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6048.5)</f>
         <v>6048.5</v>
@@ -13827,7 +13830,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E399" s="6"/>
+      <c r="E399" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2688.76)</f>
+        <v>2688.76</v>
+      </c>
       <c r="F399" s="7">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2024.5)</f>
         <v>2024.5</v>
@@ -13858,18 +13864,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E400" s="6"/>
-      <c r="F400" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G400" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H400" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="E400" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2784.41)</f>
+        <v>2784.41</v>
+      </c>
+      <c r="F400" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2597.5)</f>
+        <v>2597.5</v>
+      </c>
+      <c r="G400" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.0)</f>
+        <v>54</v>
+      </c>
+      <c r="H400" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.101851851851855)</f>
+        <v>48.10185185</v>
       </c>
     </row>
     <row r="401">
@@ -13889,7 +13898,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E401" s="6"/>
+      <c r="E401" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3123.95)</f>
+        <v>3123.95</v>
+      </c>
       <c r="F401" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13920,7 +13932,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E402" s="6"/>
+      <c r="E402" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3353.45)</f>
+        <v>3353.45</v>
+      </c>
       <c r="F402" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13951,7 +13966,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E403" s="6"/>
+      <c r="E403" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3092.86)</f>
+        <v>3092.86</v>
+      </c>
       <c r="F403" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -13982,7 +14000,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E404" s="6"/>
+      <c r="E404" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4778.57)</f>
+        <v>4778.57</v>
+      </c>
       <c r="F404" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14013,7 +14034,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E405" s="6"/>
+      <c r="E405" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4579.57)</f>
+        <v>4579.57</v>
+      </c>
       <c r="F405" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14044,7 +14068,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E406" s="6"/>
+      <c r="E406" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2688.76)</f>
+        <v>2688.76</v>
+      </c>
       <c r="F406" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14075,7 +14102,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E407" s="6"/>
+      <c r="E407" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2784.41)</f>
+        <v>2784.41</v>
+      </c>
       <c r="F407" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14106,7 +14136,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E408" s="6"/>
+      <c r="E408" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3123.95)</f>
+        <v>3123.95</v>
+      </c>
       <c r="F408" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14137,7 +14170,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E409" s="6"/>
+      <c r="E409" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3353.45)</f>
+        <v>3353.45</v>
+      </c>
       <c r="F409" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14168,7 +14204,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E410" s="6"/>
+      <c r="E410" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3092.86)</f>
+        <v>3092.86</v>
+      </c>
       <c r="F410" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14199,7 +14238,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E411" s="6"/>
+      <c r="E411" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4778.57)</f>
+        <v>4778.57</v>
+      </c>
       <c r="F411" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14230,7 +14272,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E412" s="6"/>
+      <c r="E412" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4579.57)</f>
+        <v>4579.57</v>
+      </c>
       <c r="F412" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14261,7 +14306,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E413" s="6"/>
+      <c r="E413" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2688.76)</f>
+        <v>2688.76</v>
+      </c>
       <c r="F413" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14292,7 +14340,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E414" s="6"/>
+      <c r="E414" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2784.41)</f>
+        <v>2784.41</v>
+      </c>
       <c r="F414" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14323,7 +14374,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E415" s="6"/>
+      <c r="E415" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3123.95)</f>
+        <v>3123.95</v>
+      </c>
       <c r="F415" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14354,7 +14408,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E416" s="6"/>
+      <c r="E416" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3353.45)</f>
+        <v>3353.45</v>
+      </c>
       <c r="F416" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14385,7 +14442,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E417" s="6"/>
+      <c r="E417" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3092.86)</f>
+        <v>3092.86</v>
+      </c>
       <c r="F417" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14416,7 +14476,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E418" s="6"/>
+      <c r="E418" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4778.57)</f>
+        <v>4778.57</v>
+      </c>
       <c r="F418" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14447,7 +14510,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E419" s="6"/>
+      <c r="E419" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4579.57)</f>
+        <v>4579.57</v>
+      </c>
       <c r="F419" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14478,7 +14544,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E420" s="6"/>
+      <c r="E420" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2688.76)</f>
+        <v>2688.76</v>
+      </c>
       <c r="F420" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14509,7 +14578,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E421" s="6"/>
+      <c r="E421" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2784.41)</f>
+        <v>2784.41</v>
+      </c>
       <c r="F421" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14540,7 +14612,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E422" s="6"/>
+      <c r="E422" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3123.95)</f>
+        <v>3123.95</v>
+      </c>
       <c r="F422" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14571,7 +14646,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E423" s="6"/>
+      <c r="E423" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3353.45)</f>
+        <v>3353.45</v>
+      </c>
       <c r="F423" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14602,7 +14680,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="E424" s="6"/>
+      <c r="E424" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3092.86)</f>
+        <v>3092.86</v>
+      </c>
       <c r="F424" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>
@@ -14633,7 +14714,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="E425" s="6"/>
+      <c r="E425" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4778.57)</f>
+        <v>4778.57</v>
+      </c>
       <c r="F425" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
         <v/>

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13902,17 +13902,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3123.95)</f>
         <v>3123.95</v>
       </c>
-      <c r="F401" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G401" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H401" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F401" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2935.91)</f>
+        <v>2935.91</v>
+      </c>
+      <c r="G401" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
+        <v>58</v>
+      </c>
+      <c r="H401" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.61913793103448)</f>
+        <v>50.61913793</v>
       </c>
     </row>
     <row r="402">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13936,17 +13936,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3353.45)</f>
         <v>3353.45</v>
       </c>
-      <c r="F402" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G402" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H402" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F402" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3079.5)</f>
+        <v>3079.5</v>
+      </c>
+      <c r="G402" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
+      </c>
+      <c r="H402" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.18493150684932)</f>
+        <v>42.18493151</v>
       </c>
     </row>
     <row r="403">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -13970,17 +13970,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3092.86)</f>
         <v>3092.86</v>
       </c>
-      <c r="F403" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G403" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H403" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F403" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2657.5)</f>
+        <v>2657.5</v>
+      </c>
+      <c r="G403" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.0)</f>
+        <v>65</v>
+      </c>
+      <c r="H403" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.88461538461539)</f>
+        <v>40.88461538</v>
       </c>
     </row>
     <row r="404">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -14004,17 +14004,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4778.57)</f>
         <v>4778.57</v>
       </c>
-      <c r="F404" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G404" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H404" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F404" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5130.0)</f>
+        <v>5130</v>
+      </c>
+      <c r="G404" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),115.0)</f>
+        <v>115</v>
+      </c>
+      <c r="H404" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.608695652173914)</f>
+        <v>44.60869565</v>
       </c>
     </row>
     <row r="405">
@@ -14038,17 +14038,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4579.57)</f>
         <v>4579.57</v>
       </c>
-      <c r="F405" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G405" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H405" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F405" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7023.5)</f>
+        <v>7023.5</v>
+      </c>
+      <c r="G405" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
+        <v>139</v>
+      </c>
+      <c r="H405" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.52877697841727)</f>
+        <v>50.52877698</v>
       </c>
     </row>
     <row r="406">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -14072,17 +14072,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2688.76)</f>
         <v>2688.76</v>
       </c>
-      <c r="F406" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G406" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H406" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F406" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3674.0)</f>
+        <v>3674</v>
+      </c>
+      <c r="G406" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71.0)</f>
+        <v>71</v>
+      </c>
+      <c r="H406" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.74647887323944)</f>
+        <v>51.74647887</v>
       </c>
     </row>
     <row r="407">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -14106,17 +14106,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2784.41)</f>
         <v>2784.41</v>
       </c>
-      <c r="F407" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G407" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H407" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F407" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3054.5)</f>
+        <v>3054.5</v>
+      </c>
+      <c r="G407" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.0)</f>
+        <v>65</v>
+      </c>
+      <c r="H407" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.99230769230769)</f>
+        <v>46.99230769</v>
       </c>
     </row>
     <row r="408">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -14140,17 +14140,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3123.95)</f>
         <v>3123.95</v>
       </c>
-      <c r="F408" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G408" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H408" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F408" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4457.0)</f>
+        <v>4457</v>
+      </c>
+      <c r="G408" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),77.0)</f>
+        <v>77</v>
+      </c>
+      <c r="H408" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.883116883116884)</f>
+        <v>57.88311688</v>
       </c>
     </row>
     <row r="409">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -14174,17 +14174,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3353.45)</f>
         <v>3353.45</v>
       </c>
-      <c r="F409" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G409" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H409" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F409" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1257.0)</f>
+        <v>1257</v>
+      </c>
+      <c r="G409" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
+        <v>36</v>
+      </c>
+      <c r="H409" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.916666666666664)</f>
+        <v>34.91666667</v>
       </c>
     </row>
     <row r="410">
@@ -14208,17 +14208,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3092.86)</f>
         <v>3092.86</v>
       </c>
-      <c r="F410" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G410" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H410" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F410" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1471.5)</f>
+        <v>1471.5</v>
+      </c>
+      <c r="G410" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
+        <v>37</v>
+      </c>
+      <c r="H410" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.770270270270274)</f>
+        <v>39.77027027</v>
       </c>
     </row>
     <row r="411">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -14242,17 +14242,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4778.57)</f>
         <v>4778.57</v>
       </c>
-      <c r="F411" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G411" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H411" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F411" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3689.5)</f>
+        <v>3689.5</v>
+      </c>
+      <c r="G411" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61.0)</f>
+        <v>61</v>
+      </c>
+      <c r="H411" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.48360655737705)</f>
+        <v>60.48360656</v>
       </c>
     </row>
     <row r="412">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -14276,17 +14276,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4579.57)</f>
         <v>4579.57</v>
       </c>
-      <c r="F412" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G412" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H412" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F412" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2867.5)</f>
+        <v>2867.5</v>
+      </c>
+      <c r="G412" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.0)</f>
+        <v>53</v>
+      </c>
+      <c r="H412" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.10377358490566)</f>
+        <v>54.10377358</v>
       </c>
     </row>
     <row r="413">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -14310,17 +14310,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2688.76)</f>
         <v>2688.76</v>
       </c>
-      <c r="F413" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G413" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H413" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F413" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2008.5)</f>
+        <v>2008.5</v>
+      </c>
+      <c r="G413" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
+        <v>42</v>
+      </c>
+      <c r="H413" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.82142857142857)</f>
+        <v>47.82142857</v>
       </c>
     </row>
     <row r="414">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -14344,17 +14344,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2784.41)</f>
         <v>2784.41</v>
       </c>
-      <c r="F414" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G414" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H414" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F414" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2237.0)</f>
+        <v>2237</v>
+      </c>
+      <c r="G414" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.0)</f>
+        <v>54</v>
+      </c>
+      <c r="H414" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),41.425925925925924)</f>
+        <v>41.42592593</v>
       </c>
     </row>
     <row r="415">

--- a/base_cinema.xlsx
+++ b/base_cinema.xlsx
@@ -14378,17 +14378,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3123.95)</f>
         <v>3123.95</v>
       </c>
-      <c r="F415" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G415" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H415" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F415" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1707.5)</f>
+        <v>1707.5</v>
+      </c>
+      <c r="G415" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
+      </c>
+      <c r="H415" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.8469387755102)</f>
+        <v>34.84693878</v>
       </c>
     </row>
     <row r="416">
